--- a/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
+++ b/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
@@ -514,23 +514,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F2" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="L2" t="n">
         <v>7</v>
@@ -564,23 +564,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="L3" t="n">
         <v>7</v>
@@ -614,17 +614,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="E4" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="L4" t="n">
         <v>7</v>
@@ -664,17 +664,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="E5" t="n">
         <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="L5" t="n">
         <v>7</v>
@@ -714,17 +714,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -733,13 +733,13 @@
         <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="L6" t="n">
         <v>7</v>
@@ -764,17 +764,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="E7" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
@@ -814,32 +814,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="L8" t="n">
         <v>7</v>
@@ -864,32 +864,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>6.3</v>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="G9" t="n">
-        <v>18.5</v>
+        <v>31</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.359</v>
+        <v>0.352</v>
       </c>
       <c r="L9" t="n">
         <v>7</v>
@@ -914,32 +914,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="G10" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.369</v>
+        <v>0.351</v>
       </c>
       <c r="L10" t="n">
         <v>7</v>
@@ -964,32 +964,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.376</v>
+        <v>0.352</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="E12" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F12" t="n">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="G12" t="n">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.382</v>
+        <v>0.352</v>
       </c>
       <c r="L12" t="n">
         <v>7</v>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>7.4</v>
       </c>
       <c r="E13" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F13" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.39</v>
+        <v>0.352</v>
       </c>
       <c r="L13" t="n">
         <v>7</v>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="E14" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="G14" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.396</v>
+        <v>0.354</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1174,22 +1174,22 @@
         <v>95</v>
       </c>
       <c r="F15" t="n">
-        <v>8.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G15" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.398</v>
+        <v>0.369</v>
       </c>
       <c r="L15" t="n">
         <v>7</v>
@@ -1214,32 +1214,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>96</v>
       </c>
       <c r="F16" t="n">
-        <v>4.6</v>
+        <v>7.5</v>
       </c>
       <c r="G16" t="n">
-        <v>32</v>
+        <v>23.5</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>1.35</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.397</v>
+        <v>0.386</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
@@ -1264,32 +1264,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>6.9</v>
       </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.407</v>
+        <v>0.403</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F18" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.417</v>
+        <v>0.415</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
@@ -1364,17 +1364,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.424</v>
+        <v>0.417</v>
       </c>
       <c r="L19" t="n">
         <v>7</v>
@@ -1414,17 +1414,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1433,13 +1433,13 @@
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.423</v>
+        <v>0.419</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -1464,17 +1464,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F21" t="n">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.423</v>
+        <v>0.417</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="E22" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1533,13 +1533,13 @@
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.423</v>
+        <v>0.411</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F23" t="n">
-        <v>9.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1583,13 +1583,13 @@
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.421</v>
+        <v>0.406</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="E24" t="n">
         <v>95</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1633,13 +1633,13 @@
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.418</v>
+        <v>0.406</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -1664,14 +1664,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-30T00:04:06Z</t>
+          <t>2026-10-30T06:03:42Z</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="E25" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25" t="n">
         <v>10.4</v>
@@ -1683,13 +1683,13 @@
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.413</v>
+        <v>0.407</v>
       </c>
       <c r="L25" t="n">
         <v>7</v>

--- a/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
+++ b/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
@@ -514,24 +514,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="E2" t="n">
+        <v>97</v>
+      </c>
+      <c r="F2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>98</v>
       </c>
-      <c r="F2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="L2" t="n">
         <v>7</v>
@@ -564,23 +564,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F3" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.347</v>
+        <v>0.35</v>
       </c>
       <c r="L3" t="n">
         <v>7</v>
@@ -614,17 +614,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="E4" t="n">
         <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.347</v>
+        <v>0.35</v>
       </c>
       <c r="L4" t="n">
         <v>7</v>
@@ -664,17 +664,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.347</v>
+        <v>0.35</v>
       </c>
       <c r="L5" t="n">
         <v>7</v>
@@ -714,18 +714,18 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>99</v>
+      </c>
+      <c r="F6" t="n">
         <v>5.4</v>
       </c>
-      <c r="E6" t="n">
-        <v>98</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4</v>
-      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.347</v>
+        <v>0.35</v>
       </c>
       <c r="L6" t="n">
         <v>7</v>
@@ -764,17 +764,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
@@ -814,26 +814,26 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="E8" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -864,26 +864,26 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
         <v>6.1</v>
       </c>
       <c r="G9" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -914,32 +914,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="G10" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="L10" t="n">
         <v>7</v>
@@ -964,32 +964,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="G11" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="E12" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="G12" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.352</v>
+        <v>0.358</v>
       </c>
       <c r="L12" t="n">
         <v>7</v>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="E13" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="G13" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.352</v>
+        <v>0.366</v>
       </c>
       <c r="L13" t="n">
         <v>7</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1124,22 +1124,22 @@
         <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="G14" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.354</v>
+        <v>0.37</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
@@ -1164,32 +1164,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="E15" t="n">
         <v>95</v>
       </c>
       <c r="F15" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="G15" t="n">
-        <v>43.5</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.369</v>
+        <v>0.373</v>
       </c>
       <c r="L15" t="n">
         <v>7</v>
@@ -1214,32 +1214,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="E16" t="n">
         <v>96</v>
       </c>
       <c r="F16" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>23.5</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>1.35</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.386</v>
+        <v>0.374</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
@@ -1264,32 +1264,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="E17" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F17" t="n">
-        <v>6.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.403</v>
+        <v>0.379</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -1314,32 +1314,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="E18" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F18" t="n">
         <v>7.2</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.415</v>
+        <v>0.385</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
@@ -1364,17 +1364,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F19" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.417</v>
+        <v>0.388</v>
       </c>
       <c r="L19" t="n">
         <v>7</v>
@@ -1414,17 +1414,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F20" t="n">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1433,13 +1433,13 @@
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.419</v>
+        <v>0.392</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -1464,17 +1464,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F21" t="n">
-        <v>9.9</v>
+        <v>6.6</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.417</v>
+        <v>0.395</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" t="n">
-        <v>10.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1533,13 +1533,13 @@
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.411</v>
+        <v>0.399</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1583,13 +1583,13 @@
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.406</v>
+        <v>0.401</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>95</v>
       </c>
       <c r="F24" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1633,13 +1633,13 @@
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.406</v>
+        <v>0.412</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -1664,14 +1664,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-30T06:03:42Z</t>
+          <t>2026-10-30T12:04:16Z</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F25" t="n">
         <v>10.4</v>
@@ -1683,13 +1683,13 @@
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.407</v>
+        <v>0.415</v>
       </c>
       <c r="L25" t="n">
         <v>7</v>

--- a/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
+++ b/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
@@ -514,23 +514,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.351</v>
+        <v>0.341</v>
       </c>
       <c r="L2" t="n">
         <v>7</v>
@@ -564,23 +564,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>98</v>
       </c>
       <c r="F3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.35</v>
+        <v>0.341</v>
       </c>
       <c r="L3" t="n">
         <v>7</v>
@@ -614,23 +614,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.3</v>
+        <v>4.9</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.35</v>
+        <v>0.341</v>
       </c>
       <c r="L4" t="n">
         <v>7</v>
@@ -664,17 +664,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.35</v>
+        <v>0.341</v>
       </c>
       <c r="L5" t="n">
         <v>7</v>
@@ -714,17 +714,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="E6" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="L6" t="n">
         <v>7</v>
@@ -764,17 +764,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.351</v>
+        <v>0.34</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
@@ -814,20 +814,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.352</v>
+        <v>0.34</v>
       </c>
       <c r="L8" t="n">
         <v>7</v>
@@ -864,20 +864,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="E9" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="G9" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -889,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.352</v>
+        <v>0.341</v>
       </c>
       <c r="L9" t="n">
         <v>7</v>
@@ -914,11 +914,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="E10" t="n">
         <v>84</v>
@@ -927,19 +927,19 @@
         <v>5.4</v>
       </c>
       <c r="G10" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.354</v>
+        <v>0.342</v>
       </c>
       <c r="L10" t="n">
         <v>7</v>
@@ -964,20 +964,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="G11" t="n">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.354</v>
+        <v>0.342</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F12" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="G12" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.358</v>
+        <v>0.341</v>
       </c>
       <c r="L12" t="n">
         <v>7</v>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.366</v>
+        <v>0.341</v>
       </c>
       <c r="L13" t="n">
         <v>7</v>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.37</v>
+        <v>0.341</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
@@ -1164,32 +1164,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="F15" t="n">
-        <v>10.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.373</v>
+        <v>0.341</v>
       </c>
       <c r="L15" t="n">
         <v>7</v>
@@ -1214,32 +1214,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="F16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.374</v>
+        <v>0.341</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
@@ -1264,32 +1264,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="F17" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.379</v>
+        <v>0.342</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="E18" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F18" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1333,13 +1333,13 @@
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.385</v>
+        <v>0.361</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
@@ -1364,17 +1364,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="E19" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F19" t="n">
-        <v>7.9</v>
+        <v>4.7</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.388</v>
+        <v>0.38</v>
       </c>
       <c r="L19" t="n">
         <v>7</v>
@@ -1414,17 +1414,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="E20" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1464,17 +1464,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="E21" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F21" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.395</v>
+        <v>0.397</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F22" t="n">
-        <v>8.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1533,13 +1533,13 @@
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.399</v>
+        <v>0.398</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F23" t="n">
-        <v>10.1</v>
+        <v>1.8</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1583,13 +1583,13 @@
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.401</v>
+        <v>0.404</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="E24" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" t="n">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1633,13 +1633,13 @@
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.412</v>
+        <v>0.407</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-30T12:04:16Z</t>
+          <t>2026-10-30T18:04:13Z</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="E25" t="n">
         <v>95</v>
       </c>
       <c r="F25" t="n">
-        <v>10.4</v>
+        <v>11.2</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1683,13 +1683,13 @@
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.415</v>
+        <v>0.407</v>
       </c>
       <c r="L25" t="n">
         <v>7</v>

--- a/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
+++ b/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,23 +514,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="L2" t="n">
         <v>7</v>
@@ -564,17 +564,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="L3" t="n">
         <v>7</v>
@@ -614,23 +614,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="L4" t="n">
         <v>7</v>
@@ -664,23 +664,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="L5" t="n">
         <v>7</v>
@@ -714,23 +714,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="L6" t="n">
         <v>7</v>
@@ -764,14 +764,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
         <v>2.5</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
@@ -814,20 +814,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="L8" t="n">
         <v>7</v>
@@ -864,20 +864,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="E9" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F9" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="G9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -889,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="L9" t="n">
         <v>7</v>
@@ -914,20 +914,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="E10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F10" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="G10" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="L10" t="n">
         <v>7</v>
@@ -964,32 +964,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="G11" t="n">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
@@ -1014,20 +1014,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="E12" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="G12" t="n">
-        <v>81</v>
+        <v>234</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="L12" t="n">
         <v>7</v>
@@ -1064,20 +1064,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G13" t="n">
-        <v>65</v>
+        <v>135</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="L13" t="n">
         <v>7</v>
@@ -1114,20 +1114,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>55</v>
+        <v>207</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -1139,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
@@ -1164,20 +1164,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="L15" t="n">
         <v>7</v>
@@ -1214,20 +1214,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>58</v>
+      </c>
+      <c r="F16" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="E16" t="n">
-        <v>77</v>
-      </c>
-      <c r="F16" t="n">
-        <v>8.6</v>
-      </c>
       <c r="G16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -1264,32 +1264,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="E17" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1333,13 +1333,13 @@
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.361</v>
+        <v>0.352</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
@@ -1364,17 +1364,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="E19" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F19" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.38</v>
+        <v>0.374</v>
       </c>
       <c r="L19" t="n">
         <v>7</v>
@@ -1414,17 +1414,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="E20" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1433,13 +1433,13 @@
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.392</v>
+        <v>0.387</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -1464,14 +1464,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F21" t="n">
         <v>5.8</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.397</v>
+        <v>0.398</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1539,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.398</v>
+        <v>0.401</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
@@ -1564,17 +1564,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="E23" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8</v>
+        <v>10.8</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.404</v>
+        <v>0.406</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="E24" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F24" t="n">
-        <v>5.4</v>
+        <v>10.1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1633,13 +1633,13 @@
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.407</v>
+        <v>0.408</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-30T18:04:13Z</t>
+          <t>2026-10-31T00:04:25Z</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="E25" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F25" t="n">
-        <v>11.2</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.407</v>
+        <v>0.413</v>
       </c>
       <c r="L25" t="n">
         <v>7</v>
@@ -1698,6 +1698,1206 @@
         <v>1</v>
       </c>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>94</v>
+      </c>
+      <c r="F26" t="n">
+        <v>9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>96</v>
+      </c>
+      <c r="F27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>100</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>97</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>93</v>
+      </c>
+      <c r="F29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>100</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E30" t="n">
+        <v>94</v>
+      </c>
+      <c r="F30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>94</v>
+      </c>
+      <c r="F31" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>100</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E32" t="n">
+        <v>95</v>
+      </c>
+      <c r="F32" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>100</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>96</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E34" t="n">
+        <v>97</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>96</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>53</v>
+      </c>
+      <c r="H35" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>96</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G36" t="n">
+        <v>74</v>
+      </c>
+      <c r="H36" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>95</v>
+      </c>
+      <c r="F37" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="G37" t="n">
+        <v>73</v>
+      </c>
+      <c r="H37" t="n">
+        <v>100</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>92</v>
+      </c>
+      <c r="F38" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G38" t="n">
+        <v>95</v>
+      </c>
+      <c r="H38" t="n">
+        <v>100</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>92</v>
+      </c>
+      <c r="F39" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>61</v>
+      </c>
+      <c r="H39" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="n">
+        <v>93</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>40</v>
+      </c>
+      <c r="H40" t="n">
+        <v>100</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>95</v>
+      </c>
+      <c r="F41" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" t="n">
+        <v>17</v>
+      </c>
+      <c r="H41" t="n">
+        <v>100</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>95</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>100</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E43" t="n">
+        <v>95</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>100</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E44" t="n">
+        <v>96</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>100</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E45" t="n">
+        <v>96</v>
+      </c>
+      <c r="F45" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>100</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>96</v>
+      </c>
+      <c r="F46" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>100</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>96</v>
+      </c>
+      <c r="F47" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>100</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E48" t="n">
+        <v>96</v>
+      </c>
+      <c r="F48" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>100</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:04:25Z</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E49" t="n">
+        <v>96</v>
+      </c>
+      <c r="F49" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>100</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
         <v>0</v>
       </c>
     </row>

--- a/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
+++ b/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
@@ -514,14 +514,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
         <v>8.6</v>
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -564,17 +564,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="E3" t="n">
         <v>99</v>
       </c>
       <c r="F3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -614,23 +614,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -664,23 +664,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="E5" t="n">
         <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -714,23 +714,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>6.5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -764,17 +764,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -814,20 +814,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
@@ -864,20 +864,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F9" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -914,20 +914,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F10" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="G10" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -964,23 +964,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="E11" t="n">
         <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="G11" t="n">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="H11" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
@@ -1014,20 +1014,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>8.4</v>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F12" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="G12" t="n">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="L12" t="n">
         <v>7</v>
@@ -1064,20 +1064,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="G13" t="n">
-        <v>135</v>
+        <v>268</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1114,20 +1114,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F14" t="n">
-        <v>9.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="G14" t="n">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -1164,20 +1164,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="E15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>12.2</v>
       </c>
       <c r="G15" t="n">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="L15" t="n">
         <v>7</v>
@@ -1214,20 +1214,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="E16" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F16" t="n">
-        <v>8.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="G16" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.341</v>
+        <v>0.337</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
@@ -1264,20 +1264,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>61</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
@@ -1289,7 +1289,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.341</v>
+        <v>0.337</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F18" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1333,13 +1333,13 @@
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.352</v>
+        <v>0.339</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
@@ -1364,17 +1364,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="E19" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="F19" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.374</v>
+        <v>0.349</v>
       </c>
       <c r="L19" t="n">
         <v>7</v>
@@ -1414,17 +1414,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="E20" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F20" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1433,13 +1433,13 @@
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.387</v>
+        <v>0.37</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -1464,17 +1464,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F21" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.398</v>
+        <v>0.392</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="E22" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F22" t="n">
-        <v>8.6</v>
+        <v>11.2</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1533,13 +1533,13 @@
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.401</v>
+        <v>0.397</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
@@ -1564,14 +1564,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="E23" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23" t="n">
         <v>10.8</v>
@@ -1580,16 +1580,16 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.406</v>
+        <v>0.397</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>92</v>
       </c>
       <c r="F24" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.408</v>
+        <v>0.398</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1683,13 +1683,13 @@
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.413</v>
+        <v>0.402</v>
       </c>
       <c r="L25" t="n">
         <v>7</v>
@@ -1714,17 +1714,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="E26" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.419</v>
+        <v>0.403</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1764,17 +1764,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="E27" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F27" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1783,13 +1783,13 @@
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.424</v>
+        <v>0.405</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -1814,17 +1814,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F28" t="n">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1833,13 +1833,13 @@
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.422</v>
+        <v>0.406</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -1864,17 +1864,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="E29" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F29" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1883,13 +1883,13 @@
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.421</v>
+        <v>0.412</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="E30" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F30" t="n">
-        <v>13.3</v>
+        <v>11.9</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1933,13 +1933,13 @@
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.42</v>
+        <v>0.413</v>
       </c>
       <c r="L30" t="n">
         <v>1</v>
@@ -1964,17 +1964,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="E31" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F31" t="n">
-        <v>14.8</v>
+        <v>16.6</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.416</v>
+        <v>0.413</v>
       </c>
       <c r="L31" t="n">
         <v>1</v>
@@ -2014,26 +2014,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="E32" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F32" t="n">
-        <v>13.4</v>
+        <v>15.1</v>
       </c>
       <c r="G32" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2064,32 +2064,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="E33" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F33" t="n">
-        <v>11.5</v>
+        <v>11.9</v>
       </c>
       <c r="G33" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.409</v>
+        <v>0.407</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
@@ -2114,32 +2114,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="E34" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F34" t="n">
-        <v>8.300000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="G34" t="n">
-        <v>36.3</v>
+        <v>41</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
       <c r="L34" t="n">
         <v>1</v>
@@ -2164,32 +2164,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F35" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="G35" t="n">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.407</v>
+        <v>0.399</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.4</v>
+        <v>8.1</v>
       </c>
       <c r="E36" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F36" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="G36" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.406</v>
+        <v>0.396</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
@@ -2264,32 +2264,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="E37" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F37" t="n">
-        <v>8.9</v>
+        <v>7.6</v>
       </c>
       <c r="G37" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.404</v>
+        <v>0.393</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -2314,32 +2314,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.1</v>
+        <v>8.9</v>
       </c>
       <c r="E38" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F38" t="n">
-        <v>10.7</v>
+        <v>6.6</v>
       </c>
       <c r="G38" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.401</v>
+        <v>0.391</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2364,32 +2364,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="E39" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F39" t="n">
-        <v>10.1</v>
+        <v>7.9</v>
       </c>
       <c r="G39" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.399</v>
+        <v>0.389</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -2414,32 +2414,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F40" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>58.5</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.397</v>
+        <v>0.387</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -2464,20 +2464,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.395</v>
+        <v>0.386</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2514,32 +2514,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>91</v>
+      </c>
+      <c r="F42" t="n">
         <v>9.1</v>
       </c>
-      <c r="E42" t="n">
-        <v>95</v>
-      </c>
-      <c r="F42" t="n">
-        <v>9.9</v>
-      </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.394</v>
+        <v>0.385</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -2564,17 +2564,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="E43" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F43" t="n">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2583,13 +2583,13 @@
         <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.393</v>
+        <v>0.384</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
@@ -2614,17 +2614,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="E44" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F44" t="n">
-        <v>6.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.392</v>
+        <v>0.382</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -2664,17 +2664,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="E45" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F45" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2683,13 +2683,13 @@
         <v>100</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.392</v>
+        <v>0.381</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -2714,32 +2714,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F46" t="n">
         <v>7.1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.394</v>
+        <v>0.381</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
@@ -2764,17 +2764,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="E47" t="n">
         <v>96</v>
       </c>
       <c r="F47" t="n">
-        <v>6.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2783,13 +2783,13 @@
         <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.396</v>
+        <v>0.382</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -2814,17 +2814,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="E48" t="n">
         <v>96</v>
       </c>
       <c r="F48" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2833,13 +2833,13 @@
         <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4</v>
+        <v>0.381</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
@@ -2864,17 +2864,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-31T00:04:25Z</t>
+          <t>2026-10-31T06:03:38Z</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="E49" t="n">
         <v>96</v>
       </c>
       <c r="F49" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.399</v>
+        <v>0.382</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>

--- a/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
+++ b/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
@@ -514,32 +514,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="E2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F2" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.343</v>
+        <v>0.35</v>
       </c>
       <c r="L2" t="n">
         <v>7</v>
@@ -564,23 +564,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>98</v>
+      </c>
+      <c r="F3" t="n">
         <v>5.8</v>
       </c>
-      <c r="E3" t="n">
-        <v>99</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7.9</v>
-      </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.343</v>
+        <v>0.35</v>
       </c>
       <c r="L3" t="n">
         <v>7</v>
@@ -614,23 +614,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.343</v>
+        <v>0.35</v>
       </c>
       <c r="L4" t="n">
         <v>7</v>
@@ -664,23 +664,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="E5" t="n">
         <v>99</v>
       </c>
       <c r="F5" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.343</v>
+        <v>0.35</v>
       </c>
       <c r="L5" t="n">
         <v>7</v>
@@ -714,17 +714,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F6" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.342</v>
+        <v>0.349</v>
       </c>
       <c r="L6" t="n">
         <v>7</v>
@@ -764,17 +764,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="E7" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F7" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.342</v>
+        <v>0.349</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
@@ -814,20 +814,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.342</v>
+        <v>0.349</v>
       </c>
       <c r="L8" t="n">
         <v>7</v>
@@ -864,11 +864,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="E9" t="n">
         <v>87</v>
@@ -877,7 +877,7 @@
         <v>6.5</v>
       </c>
       <c r="G9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
@@ -889,7 +889,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.342</v>
+        <v>0.349</v>
       </c>
       <c r="L9" t="n">
         <v>7</v>
@@ -914,20 +914,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F10" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="G10" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.341</v>
+        <v>0.348</v>
       </c>
       <c r="L10" t="n">
         <v>7</v>
@@ -964,32 +964,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F11" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="G11" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.341</v>
+        <v>0.347</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
@@ -1014,20 +1014,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F12" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="G12" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.34</v>
+        <v>0.347</v>
       </c>
       <c r="L12" t="n">
         <v>7</v>
@@ -1064,20 +1064,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="G13" t="n">
-        <v>268</v>
+        <v>134</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.34</v>
+        <v>0.346</v>
       </c>
       <c r="L13" t="n">
         <v>7</v>
@@ -1114,20 +1114,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>153</v>
+        <v>71</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -1139,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.339</v>
+        <v>0.347</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
@@ -1164,20 +1164,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="F15" t="n">
-        <v>12.2</v>
+        <v>9.4</v>
       </c>
       <c r="G15" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.338</v>
+        <v>0.346</v>
       </c>
       <c r="L15" t="n">
         <v>7</v>
@@ -1214,20 +1214,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.4</v>
+        <v>9.5</v>
       </c>
       <c r="E16" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="F16" t="n">
-        <v>11.9</v>
+        <v>10.1</v>
       </c>
       <c r="G16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.337</v>
+        <v>0.347</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
@@ -1264,32 +1264,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="E17" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>9.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.337</v>
+        <v>0.35</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -1314,32 +1314,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.339</v>
+        <v>0.353</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
@@ -1364,17 +1364,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9.9</v>
+        <v>8.6</v>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.349</v>
+        <v>0.361</v>
       </c>
       <c r="L19" t="n">
         <v>7</v>
@@ -1414,17 +1414,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F20" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1433,13 +1433,13 @@
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.37</v>
+        <v>0.378</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -1464,17 +1464,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="E21" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F21" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.392</v>
+        <v>0.386</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1524,7 +1524,7 @@
         <v>94</v>
       </c>
       <c r="F22" t="n">
-        <v>11.2</v>
+        <v>6.8</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1533,13 +1533,13 @@
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.397</v>
+        <v>0.388</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1574,22 +1574,22 @@
         <v>94</v>
       </c>
       <c r="F23" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.397</v>
+        <v>0.386</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="E24" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F24" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.398</v>
+        <v>0.385</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F25" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1683,13 +1683,13 @@
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.402</v>
+        <v>0.383</v>
       </c>
       <c r="L25" t="n">
         <v>7</v>
@@ -1714,17 +1714,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="E26" t="n">
         <v>92</v>
       </c>
       <c r="F26" t="n">
-        <v>7.6</v>
+        <v>10.1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1733,13 +1733,13 @@
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.403</v>
+        <v>0.382</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1764,17 +1764,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>8.5</v>
       </c>
       <c r="E27" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F27" t="n">
-        <v>8.6</v>
+        <v>11.9</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1783,13 +1783,13 @@
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.405</v>
+        <v>0.381</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -1814,17 +1814,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="E28" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F28" t="n">
-        <v>10.4</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.406</v>
+        <v>0.38</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -1864,17 +1864,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="E29" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F29" t="n">
-        <v>11.2</v>
+        <v>12.6</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1889,7 +1889,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.412</v>
+        <v>0.38</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F30" t="n">
-        <v>11.9</v>
+        <v>13.7</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.413</v>
+        <v>0.381</v>
       </c>
       <c r="L30" t="n">
         <v>1</v>
@@ -1964,17 +1964,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="E31" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F31" t="n">
-        <v>16.6</v>
+        <v>18.7</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.413</v>
+        <v>0.381</v>
       </c>
       <c r="L31" t="n">
         <v>1</v>
@@ -2014,17 +2014,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="E32" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F32" t="n">
-        <v>15.1</v>
+        <v>14.4</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -2033,13 +2033,13 @@
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.412</v>
+        <v>0.38</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2064,32 +2064,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>7.4</v>
       </c>
       <c r="E33" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F33" t="n">
-        <v>11.9</v>
+        <v>11.2</v>
       </c>
       <c r="G33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.407</v>
+        <v>0.382</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
@@ -2114,32 +2114,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="E34" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F34" t="n">
-        <v>6.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.403</v>
+        <v>0.381</v>
       </c>
       <c r="L34" t="n">
         <v>1</v>
@@ -2164,32 +2164,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="E35" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F35" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.399</v>
+        <v>0.38</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="E36" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F36" t="n">
-        <v>6.8</v>
+        <v>10.4</v>
       </c>
       <c r="G36" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.396</v>
+        <v>0.379</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
@@ -2264,32 +2264,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F37" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="G37" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.393</v>
+        <v>0.378</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -2314,32 +2314,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8.9</v>
+        <v>7.6</v>
       </c>
       <c r="E38" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F38" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="G38" t="n">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.391</v>
+        <v>0.377</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2364,32 +2364,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D39" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>95</v>
+      </c>
+      <c r="F39" t="n">
         <v>9.4</v>
       </c>
-      <c r="E39" t="n">
-        <v>86</v>
-      </c>
-      <c r="F39" t="n">
-        <v>7.9</v>
-      </c>
       <c r="G39" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.389</v>
+        <v>0.375</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -2414,32 +2414,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="E40" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="F40" t="n">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="G40" t="n">
-        <v>58.5</v>
+        <v>18</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.387</v>
+        <v>0.374</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -2464,32 +2464,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="E41" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F41" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="G41" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.386</v>
+        <v>0.373</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2514,20 +2514,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="E42" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F42" t="n">
-        <v>9.1</v>
+        <v>5.8</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -2539,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.385</v>
+        <v>0.372</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -2564,17 +2564,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="E43" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F43" t="n">
-        <v>9.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2583,13 +2583,13 @@
         <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.384</v>
+        <v>0.371</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
@@ -2614,17 +2614,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F44" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.382</v>
+        <v>0.371</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -2664,17 +2664,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="E45" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F45" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.381</v>
+        <v>0.37</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -2714,18 +2714,18 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D46" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>93</v>
+      </c>
+      <c r="F46" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="E46" t="n">
-        <v>94</v>
-      </c>
-      <c r="F46" t="n">
-        <v>7.1</v>
-      </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
@@ -2733,13 +2733,13 @@
         <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.381</v>
+        <v>0.37</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
@@ -2764,17 +2764,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="E47" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F47" t="n">
-        <v>9.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2783,13 +2783,13 @@
         <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.382</v>
+        <v>0.371</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -2814,17 +2814,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="E48" t="n">
         <v>96</v>
       </c>
       <c r="F48" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2833,13 +2833,13 @@
         <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.381</v>
+        <v>0.373</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
@@ -2864,17 +2864,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-31T06:03:38Z</t>
+          <t>2026-10-31T12:03:47Z</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E49" t="n">
         <v>96</v>
       </c>
       <c r="F49" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2883,13 +2883,13 @@
         <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.382</v>
+        <v>0.375</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>

--- a/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
+++ b/podaci/vremenska_prognoza/excel/vremenska_prognoza_2026-11.xlsx
@@ -514,32 +514,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F2" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="L2" t="n">
         <v>7</v>
@@ -564,7 +564,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -574,7 +574,7 @@
         <v>98</v>
       </c>
       <c r="F3" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="L3" t="n">
         <v>7</v>
@@ -614,17 +614,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="E4" t="n">
         <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="L4" t="n">
         <v>7</v>
@@ -664,14 +664,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="E5" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.35</v>
+        <v>0.354</v>
       </c>
       <c r="L5" t="n">
         <v>7</v>
@@ -714,17 +714,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="E6" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.349</v>
+        <v>0.355</v>
       </c>
       <c r="L6" t="n">
         <v>7</v>
@@ -764,14 +764,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="E7" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F7" t="n">
         <v>5.4</v>
@@ -783,13 +783,13 @@
         <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.349</v>
+        <v>0.354</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
@@ -814,32 +814,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>6.2</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F8" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.349</v>
+        <v>0.355</v>
       </c>
       <c r="L8" t="n">
         <v>7</v>
@@ -864,32 +864,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="E9" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F9" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="G9" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="H9" t="n">
         <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.349</v>
+        <v>0.357</v>
       </c>
       <c r="L9" t="n">
         <v>7</v>
@@ -914,32 +914,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="G10" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="H10" t="n">
         <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.348</v>
+        <v>0.36</v>
       </c>
       <c r="L10" t="n">
         <v>7</v>
@@ -964,32 +964,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
         <v>6.8</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="H11" t="n">
         <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.347</v>
+        <v>0.365</v>
       </c>
       <c r="L11" t="n">
         <v>7</v>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="E12" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F12" t="n">
         <v>7.9</v>
       </c>
       <c r="G12" t="n">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="H12" t="n">
         <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.347</v>
+        <v>0.366</v>
       </c>
       <c r="L12" t="n">
         <v>7</v>
@@ -1064,20 +1064,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F13" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="G13" t="n">
-        <v>134</v>
+        <v>54</v>
       </c>
       <c r="H13" t="n">
         <v>100</v>
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.346</v>
+        <v>0.366</v>
       </c>
       <c r="L13" t="n">
         <v>7</v>
@@ -1114,20 +1114,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="G14" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -1139,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.347</v>
+        <v>0.365</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
@@ -1164,20 +1164,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="E15" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F15" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="G15" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="H15" t="n">
         <v>100</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.346</v>
+        <v>0.364</v>
       </c>
       <c r="L15" t="n">
         <v>7</v>
@@ -1214,20 +1214,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="E16" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>10.1</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H16" t="n">
         <v>100</v>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.347</v>
+        <v>0.364</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
@@ -1264,32 +1264,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F17" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.35</v>
+        <v>0.363</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F18" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1333,13 +1333,13 @@
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.353</v>
+        <v>0.363</v>
       </c>
       <c r="L18" t="n">
         <v>7</v>
@@ -1364,17 +1364,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.361</v>
+        <v>0.363</v>
       </c>
       <c r="L19" t="n">
         <v>7</v>
@@ -1414,14 +1414,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F20" t="n">
         <v>5</v>
@@ -1433,13 +1433,13 @@
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.378</v>
+        <v>0.362</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -1464,17 +1464,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F21" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.386</v>
+        <v>0.364</v>
       </c>
       <c r="L21" t="n">
         <v>7</v>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F22" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1533,13 +1533,13 @@
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.388</v>
+        <v>0.367</v>
       </c>
       <c r="L22" t="n">
         <v>7</v>
@@ -1564,14 +1564,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F23" t="n">
         <v>7.6</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.386</v>
+        <v>0.366</v>
       </c>
       <c r="L23" t="n">
         <v>7</v>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F24" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.385</v>
+        <v>0.365</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -1664,17 +1664,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F25" t="n">
-        <v>10.4</v>
+        <v>6.1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.383</v>
+        <v>0.365</v>
       </c>
       <c r="L25" t="n">
         <v>7</v>
@@ -1714,17 +1714,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>8.6</v>
       </c>
       <c r="E26" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F26" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.382</v>
+        <v>0.366</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1764,17 +1764,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="E27" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F27" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1783,13 +1783,13 @@
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.381</v>
+        <v>0.368</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -1814,17 +1814,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>11.2</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1833,13 +1833,13 @@
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -1864,17 +1864,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F29" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1883,13 +1883,13 @@
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.38</v>
+        <v>0.371</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -1914,17 +1914,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F30" t="n">
-        <v>13.7</v>
+        <v>9.4</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1933,13 +1933,13 @@
         <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.381</v>
+        <v>0.372</v>
       </c>
       <c r="L30" t="n">
         <v>1</v>
@@ -1964,17 +1964,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>7.8</v>
       </c>
       <c r="E31" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F31" t="n">
-        <v>18.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.381</v>
+        <v>0.373</v>
       </c>
       <c r="L31" t="n">
         <v>1</v>
@@ -2014,17 +2014,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>7.5</v>
       </c>
       <c r="E32" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F32" t="n">
-        <v>14.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -2033,13 +2033,13 @@
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.38</v>
+        <v>0.374</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2064,32 +2064,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="E33" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F33" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.382</v>
+        <v>0.374</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
@@ -2114,32 +2114,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="E34" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F34" t="n">
-        <v>8.300000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="G34" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H34" t="n">
         <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.381</v>
+        <v>0.374</v>
       </c>
       <c r="L34" t="n">
         <v>1</v>
@@ -2164,32 +2164,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="E35" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F35" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="G35" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.38</v>
+        <v>0.374</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F36" t="n">
-        <v>10.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.379</v>
+        <v>0.374</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
@@ -2264,20 +2264,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="E37" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F37" t="n">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="G37" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
@@ -2289,7 +2289,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.378</v>
+        <v>0.373</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -2314,32 +2314,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="E38" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F38" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="G38" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H38" t="n">
         <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.377</v>
+        <v>0.372</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2364,32 +2364,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="E39" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F39" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="G39" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="H39" t="n">
         <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.375</v>
+        <v>0.371</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -2414,32 +2414,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="E40" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F40" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="G40" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.374</v>
+        <v>0.37</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -2464,20 +2464,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="E41" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="G41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H41" t="n">
         <v>100</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.373</v>
+        <v>0.369</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2514,20 +2514,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="E42" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F42" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
@@ -2539,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.372</v>
+        <v>0.368</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -2564,17 +2564,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F43" t="n">
-        <v>4.7</v>
+        <v>7.9</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
@@ -2614,17 +2614,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="E44" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F44" t="n">
-        <v>7.9</v>
+        <v>6.1</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.371</v>
+        <v>0.366</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -2664,17 +2664,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="E45" t="n">
         <v>94</v>
       </c>
       <c r="F45" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.37</v>
+        <v>0.366</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -2714,17 +2714,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="E46" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F46" t="n">
-        <v>8.699999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.37</v>
+        <v>0.366</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
@@ -2764,17 +2764,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="E47" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F47" t="n">
-        <v>7.6</v>
+        <v>10.1</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2783,13 +2783,13 @@
         <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -2814,17 +2814,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="E48" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F48" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2833,13 +2833,13 @@
         <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.373</v>
+        <v>0.367</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
@@ -2864,17 +2864,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-31T12:03:47Z</t>
+          <t>2026-10-31T18:03:53Z</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="E49" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F49" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2883,13 +2883,13 @@
         <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.375</v>
+        <v>0.367</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>
